--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65637억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 64655억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 64668억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 63916억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 63012억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 62370억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 61037억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -918,7 +918,7 @@
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 365억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 366억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
@@ -1755,43 +1755,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65637억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 64655억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 64668억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 63916억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 63012억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 62370억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 61037억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2222,7 +2222,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 365억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 366억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6515,26 +6515,26 @@
         <v>0.319861</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.208026</v>
+        <v>0.208012</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.021069</v>
+        <v>0.034026</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.019504</v>
+        <v>-0.019802</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.033231</v>
+        <v>-0.033529</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.039993</v>
+        <v>-0.040282</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.035339</v>
+        <v>-0.047728</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.056149</v>
+        <v>-0.056166</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6664,29 +6664,29 @@
         <v>0.07949000000000001</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.079489</v>
+        <v>0.07949000000000001</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.079489</v>
+        <v>0.0795</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.079497</v>
+        <v>0.079498</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.079496</v>
+        <v>0.079497</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.079494</v>
+        <v>0.079495</v>
       </c>
       <c r="AM22" s="24" t="n">
+        <v>0.079499</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.079498</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.079497</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6825,23 +6825,23 @@
         <v>0.036886</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.03689</v>
+        <v>0.036889</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036886</v>
+        <v>0.036885</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036886</v>
+        <v>0.036885</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036889</v>
+        <v>0.036888</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036888</v>
+        <v>0.036887</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7406,7 +7406,7 @@
         <v>0.270125</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.269961</v>
+        <v>0.270021</v>
       </c>
       <c r="AI27" s="24" t="n">
         <v>0.269889</v>
@@ -7416,16 +7416,16 @@
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.270033</v>
+        <v>0.270115</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.269924</v>
+        <v>0.270006</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.269963</v>
+        <v>0.270046</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.270059</v>
+        <v>0.269831</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7561,26 +7561,26 @@
         <v>0.399755</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.399917</v>
+        <v>0.400082</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.400082</v>
+        <v>0.400247</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.400166</v>
+        <v>0.399917</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.399833</v>
+        <v>0.4</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.400084</v>
+        <v>0.399832</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.399914</v>
+        <v>0.400086</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7793,23 +7793,23 @@
       <c r="AF30" s="31" t="n"/>
       <c r="AG30" s="31" t="n"/>
       <c r="AH30" s="24" t="n">
-        <v>0.016489</v>
+        <v>0.026636</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>-0.015233</v>
+        <v>-0.015479</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>-0.026238</v>
+        <v>-0.026484</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>-0.031566</v>
+        <v>-0.031813</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>-0.027702</v>
+        <v>-0.037559</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>-0.044162</v>
+        <v>-0.044173</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8046,23 +8046,23 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AH32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AH32" s="29" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
         <v>0</v>
@@ -8171,29 +8171,29 @@
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
         <v>-0.01</v>
       </c>
       <c r="AM33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8521,23 +8521,23 @@
         <v>0.077331</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.070989</v>
+        <v>0.071868</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.06655700000000001</v>
+        <v>0.06647500000000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.061942</v>
+        <v>0.06187</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.057773</v>
+        <v>0.05771</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.054298</v>
+        <v>0.054242</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.050656</v>
+        <v>0.050628</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9168,20 +9168,20 @@
       <c r="AG42" s="31" t="n"/>
       <c r="AH42" s="31" t="n"/>
       <c r="AI42" s="24" t="n">
-        <v>-0.277607</v>
+        <v>-0.279652</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>0.517647</v>
+        <v>0.513369</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>0.003514</v>
+        <v>0.000703</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.0163</v>
+        <v>0.01919</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.025478</v>
+        <v>0.028389</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9591,23 +9591,23 @@
         <v>0.036886</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.03689</v>
+        <v>0.036889</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.036886</v>
+        <v>0.036885</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.036886</v>
+        <v>0.036885</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.036889</v>
+        <v>0.036888</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.036888</v>
+        <v>0.036887</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -30917,7 +30917,7 @@
         <v>14.23</v>
       </c>
       <c r="AH33" s="20" t="n">
-        <v>14.11</v>
+        <v>14.07</v>
       </c>
       <c r="AI33" s="20">
         <f>IFERROR(AD33*(1+변수!AI42),"")</f>

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$94</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$103</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$89</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66113억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 67102억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 69348억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 73275억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 77533억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 82494억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 87565억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 92791억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 96850억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 341억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 343억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 366억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 370억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 390억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 399억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 414억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 430억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 438억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 463억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 462억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 497억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1749,49 +1749,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66113억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 67102억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 69348억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 73275억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 77533억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 82494억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 87565억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 92791억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 96850억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2216,37 +2216,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 341억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 343억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 366억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 370억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 390억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 399억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 414억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 430억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 438억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 463억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 462억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 497억 × 2.00% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4329,7 +4329,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.4, "op_wape_pct": 90.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 501.41, "rev_act": 560.09, "op_pred": 10.02, "op_act": 27.88}, {"q": "2025Q4", "rev_pred": 542.95, "rev_act": 539.23, "op_pred": 10.85, "op_act": -0.36}, {"q": "2026Q1", "rev_pred": 503.83, "rev_act": 661.2, "op_pred": 10.07, "op_act": 81.6}, {"q": "2026Q2", "rev_pred": 529.64, "rev_act": 717.21, "op_pred": 10.59, "op_act": 92.26}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.4, "op_wape_pct": 90.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 501.41, "rev_act": 560.09, "op_pred": 10.02, "op_act": 27.88}, {"q": "2025Q4", "rev_pred": 542.95, "rev_act": 539.23, "op_pred": 10.85, "op_act": -0.36}, {"q": "2026Q1", "rev_pred": 503.83, "rev_act": 661.2, "op_pred": 10.07, "op_act": 81.6}, {"q": "2026Q2", "rev_pred": 529.64, "rev_act": 717.21, "op_pred": 10.59, "op_act": 92.26}]}</t>
         </is>
       </c>
     </row>
@@ -6512,29 +6512,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.319861</v>
+        <v>0.339613</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.208012</v>
+        <v>0.276333</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.034026</v>
+        <v>0.157195</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.019802</v>
+        <v>0.175546</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.033529</v>
+        <v>0.229376</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.040282</v>
+        <v>0.262683</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.047728</v>
+        <v>0.266338</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.056166</v>
+        <v>0.249162</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6661,32 +6661,32 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.07949000000000001</v>
+        <v>0.07949199999999999</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.07949000000000001</v>
+        <v>0.079495</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.0795</v>
+        <v>0.079495</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.079498</v>
+        <v>0.079497</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.079497</v>
+        <v>0.07949199999999999</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.079495</v>
+        <v>0.07949100000000001</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.079499</v>
+        <v>0.079496</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.079498</v>
+        <v>0.079496</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6816,32 +6816,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
+        <v>0.036884</v>
+      </c>
+      <c r="AG23" s="24" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="AH23" s="24" t="n">
+        <v>0.036889</v>
+      </c>
+      <c r="AI23" s="24" t="n">
         <v>0.036886</v>
-      </c>
-      <c r="AG23" s="24" t="n">
-        <v>0.036888</v>
-      </c>
-      <c r="AH23" s="24" t="n">
-        <v>0.036886</v>
-      </c>
-      <c r="AI23" s="24" t="n">
-        <v>0.036889</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036885</v>
+        <v>0.03689</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036885</v>
+        <v>0.036882</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036888</v>
+        <v>0.036886</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036887</v>
+        <v>0.036881</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7093,29 +7093,29 @@
         <v>1.46</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AH25" s="29" t="n">
         <v>1.71</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7400,32 +7400,32 @@
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.270134</v>
+        <v>0.270144</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.270125</v>
+        <v>0.269873</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.270021</v>
+        <v>0.270126</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.269889</v>
+        <v>0.269949</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.270115</v>
+        <v>0.269924</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.270006</v>
+        <v>0.269987</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.270046</v>
+        <v>0.269952</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.269831</v>
+        <v>0.269944</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7555,32 +7555,32 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.400244</v>
+        <v>0.40008</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.399755</v>
+        <v>0.399845</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.400082</v>
+        <v>0.4</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.400247</v>
+        <v>0.399862</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.399917</v>
+        <v>0.399935</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.4</v>
+        <v>0.400122</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.399832</v>
+        <v>0.400058</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.400086</v>
+        <v>0.40011</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7793,23 +7793,23 @@
       <c r="AF30" s="31" t="n"/>
       <c r="AG30" s="31" t="n"/>
       <c r="AH30" s="24" t="n">
-        <v>0.026636</v>
+        <v>0.123034</v>
       </c>
       <c r="AI30" s="24" t="n">
-        <v>-0.015479</v>
+        <v>0.138575</v>
       </c>
       <c r="AJ30" s="25" t="n"/>
       <c r="AK30" s="24" t="n">
-        <v>-0.026484</v>
+        <v>0.181774</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>-0.031813</v>
+        <v>0.209396</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>-0.037559</v>
+        <v>0.214592</v>
       </c>
       <c r="AN30" s="24" t="n">
-        <v>-0.044173</v>
+        <v>0.203064</v>
       </c>
       <c r="AO30" s="25" t="n"/>
     </row>
@@ -8043,20 +8043,20 @@
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AG32" s="29" t="n">
+      <c r="AH32" s="29" t="n">
         <v>0.01</v>
       </c>
-      <c r="AH32" s="29" t="n">
+      <c r="AI32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AI32" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>0</v>
@@ -8171,29 +8171,29 @@
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AM33" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AN33" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN33" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8515,29 +8515,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.08407199999999999</v>
+        <v>0.08527</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.077331</v>
+        <v>0.081409</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.071868</v>
+        <v>0.079627</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.06647500000000001</v>
+        <v>0.07807600000000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.06187</v>
+        <v>0.07713299999999999</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.05771</v>
+        <v>0.076053</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.054242</v>
+        <v>0.074959</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.050628</v>
+        <v>0.07289</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9168,20 +9168,20 @@
       <c r="AG42" s="31" t="n"/>
       <c r="AH42" s="31" t="n"/>
       <c r="AI42" s="24" t="n">
-        <v>-0.279652</v>
+        <v>-0.340491</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>0.513369</v>
+        <v>0.310825</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>0.000703</v>
+        <v>-0.175966</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.01919</v>
+        <v>-0.193165</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.028389</v>
+        <v>-0.203876</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9297,7 +9297,7 @@
         <v>-0.025641</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.025641</v>
+        <v>-0.051282</v>
       </c>
       <c r="AN43" s="24" t="n">
         <v>-0.026316</v>
@@ -9582,32 +9582,32 @@
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
+        <v>0.036884</v>
+      </c>
+      <c r="AG45" s="24" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="AH45" s="24" t="n">
+        <v>0.036889</v>
+      </c>
+      <c r="AI45" s="24" t="n">
         <v>0.036886</v>
-      </c>
-      <c r="AG45" s="24" t="n">
-        <v>0.036888</v>
-      </c>
-      <c r="AH45" s="24" t="n">
-        <v>0.036886</v>
-      </c>
-      <c r="AI45" s="24" t="n">
-        <v>0.036889</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.036885</v>
+        <v>0.03689</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.036885</v>
+        <v>0.036882</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.036888</v>
+        <v>0.036886</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.036887</v>
+        <v>0.036881</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10102,7 +10102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AO103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12528,7 +12528,12 @@
       <c r="X25" s="18" t="n">
         <v>111900</v>
       </c>
-      <c r="Z25" s="9" t="n"/>
+      <c r="Y25" s="18" t="n">
+        <v>88400</v>
+      </c>
+      <c r="Z25" s="34" t="n">
+        <v>88400</v>
+      </c>
       <c r="AB25" s="5" t="n"/>
       <c r="AC25" s="10" t="n"/>
       <c r="AD25" s="10" t="n"/>
@@ -13267,7 +13272,12 @@
       <c r="W33" s="18" t="n">
         <v>17000</v>
       </c>
-      <c r="Z33" s="9" t="n"/>
+      <c r="Y33" s="18" t="n">
+        <v>49174.78</v>
+      </c>
+      <c r="Z33" s="34" t="n">
+        <v>49174.78</v>
+      </c>
       <c r="AB33" s="5" t="n"/>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
@@ -14509,7 +14519,12 @@
       <c r="X48" s="18" t="n">
         <v>111900</v>
       </c>
-      <c r="Z48" s="9" t="n"/>
+      <c r="Y48" s="18" t="n">
+        <v>137574.78</v>
+      </c>
+      <c r="Z48" s="34" t="n">
+        <v>137574.78</v>
+      </c>
       <c r="AB48" s="5" t="n"/>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -14594,7 +14609,12 @@
       <c r="X49" s="18" t="n">
         <v>101691.42</v>
       </c>
-      <c r="Z49" s="9" t="n"/>
+      <c r="Y49" s="18" t="n">
+        <v>106903.94</v>
+      </c>
+      <c r="Z49" s="34" t="n">
+        <v>106903.94</v>
+      </c>
       <c r="AB49" s="5" t="n"/>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -16623,78 +16643,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>23553.35</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F74" s="9" t="n"/>
-      <c r="G74" s="18" t="n">
-        <v>-6348.39</v>
-      </c>
-      <c r="H74" s="18" t="n">
-        <v>-10704.54</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <v>219.35</v>
-      </c>
-      <c r="J74" s="18" t="n">
-        <v>7160.8</v>
-      </c>
-      <c r="K74" s="34" t="n">
-        <v>-9672.780000000001</v>
-      </c>
-      <c r="L74" s="18" t="n">
-        <v>-12823.7</v>
-      </c>
-      <c r="M74" s="18" t="n">
-        <v>1188.99</v>
-      </c>
-      <c r="N74" s="18" t="n">
-        <v>-1097.21</v>
-      </c>
-      <c r="O74" s="18" t="n">
-        <v>17935.62</v>
-      </c>
-      <c r="P74" s="34" t="n">
-        <v>5203.7</v>
-      </c>
-      <c r="Q74" s="18" t="n">
-        <v>-6817.31</v>
-      </c>
-      <c r="R74" s="18" t="n">
-        <v>-141.65</v>
-      </c>
-      <c r="S74" s="18" t="n">
-        <v>7484.89</v>
-      </c>
-      <c r="T74" s="18" t="n">
-        <v>-4376.7</v>
-      </c>
-      <c r="U74" s="34" t="n">
-        <v>-3850.77</v>
-      </c>
-      <c r="V74" s="18" t="n">
-        <v>8809.92</v>
-      </c>
-      <c r="W74" s="18" t="n">
-        <v>-4361.97</v>
-      </c>
-      <c r="X74" s="18" t="n">
-        <v>-1827.95</v>
-      </c>
-      <c r="Y74" s="18" t="n">
-        <v>-5555.15</v>
-      </c>
-      <c r="Z74" s="34" t="n">
-        <v>-2935.15</v>
-      </c>
-      <c r="AA74" s="18" t="n">
-        <v>9937.16</v>
-      </c>
+      <c r="K74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
+      <c r="U74" s="9" t="n"/>
+      <c r="Z74" s="9" t="n"/>
       <c r="AB74" s="19" t="n">
-        <v>3266.37</v>
+        <v>149.41</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -16716,69 +16674,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>1278.99</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F75" s="9" t="n"/>
-      <c r="G75" s="18" t="n">
-        <v>1295.36</v>
-      </c>
-      <c r="H75" s="18" t="n">
-        <v>1319.42</v>
-      </c>
-      <c r="I75" s="18" t="n">
-        <v>1299.61</v>
-      </c>
-      <c r="J75" s="18" t="n">
-        <v>1311.88</v>
-      </c>
-      <c r="K75" s="34" t="n">
-        <v>5226.27</v>
-      </c>
-      <c r="L75" s="18" t="n">
-        <v>1306.27</v>
-      </c>
-      <c r="M75" s="18" t="n">
-        <v>1315.98</v>
-      </c>
-      <c r="N75" s="18" t="n">
-        <v>1248.51</v>
-      </c>
-      <c r="O75" s="18" t="n">
-        <v>1256.47</v>
-      </c>
-      <c r="P75" s="34" t="n">
-        <v>5127.23</v>
-      </c>
-      <c r="Q75" s="18" t="n">
-        <v>1098.99</v>
-      </c>
-      <c r="R75" s="18" t="n">
-        <v>1073.65</v>
-      </c>
-      <c r="S75" s="18" t="n">
-        <v>1092.27</v>
-      </c>
-      <c r="T75" s="18" t="n">
-        <v>1114.48</v>
-      </c>
-      <c r="U75" s="34" t="n">
-        <v>4379.39</v>
-      </c>
-      <c r="V75" s="18" t="n">
-        <v>851.96</v>
-      </c>
-      <c r="W75" s="18" t="n">
-        <v>866.21</v>
-      </c>
-      <c r="X75" s="18" t="n">
-        <v>843.39</v>
-      </c>
+      <c r="K75" s="9" t="n"/>
+      <c r="P75" s="9" t="n"/>
+      <c r="U75" s="9" t="n"/>
       <c r="Z75" s="9" t="n"/>
-      <c r="AB75" s="5" t="n"/>
+      <c r="AB75" s="19" t="n">
+        <v>1144.75</v>
+      </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
@@ -16799,69 +16705,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>20.36</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F76" s="9" t="n"/>
-      <c r="G76" s="18" t="n">
-        <v>19.59</v>
-      </c>
-      <c r="H76" s="18" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="I76" s="18" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="K76" s="34" t="n">
-        <v>73.08</v>
-      </c>
-      <c r="L76" s="18" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="M76" s="18" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="N76" s="18" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="P76" s="34" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="Q76" s="18" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="R76" s="18" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="S76" s="18" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="T76" s="18" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="U76" s="34" t="n">
-        <v>32.95</v>
-      </c>
-      <c r="V76" s="18" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="W76" s="18" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="X76" s="18" t="n">
-        <v>7.57</v>
-      </c>
+      <c r="K76" s="9" t="n"/>
+      <c r="P76" s="9" t="n"/>
+      <c r="U76" s="9" t="n"/>
       <c r="Z76" s="9" t="n"/>
-      <c r="AB76" s="5" t="n"/>
+      <c r="AB76" s="19" t="n">
+        <v>435.57</v>
+      </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
@@ -16882,78 +16736,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>-11.17</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
-      <c r="G77" s="18" t="n">
-        <v>-1404.33</v>
-      </c>
-      <c r="H77" s="18" t="n">
-        <v>-1727.34</v>
-      </c>
-      <c r="I77" s="18" t="n">
-        <v>-1500.5</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>-17.19</v>
-      </c>
-      <c r="K77" s="34" t="n">
-        <v>-4649.36</v>
-      </c>
-      <c r="L77" s="18" t="n">
-        <v>-1391.98</v>
-      </c>
-      <c r="M77" s="18" t="n">
-        <v>-1852.12</v>
-      </c>
-      <c r="N77" s="18" t="n">
-        <v>-762.86</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>-238.98</v>
-      </c>
-      <c r="P77" s="34" t="n">
-        <v>-4245.94</v>
-      </c>
-      <c r="Q77" s="18" t="n">
-        <v>-11.53</v>
-      </c>
-      <c r="R77" s="18" t="n">
-        <v>-210.94</v>
-      </c>
-      <c r="S77" s="18" t="n">
-        <v>-391.63</v>
-      </c>
-      <c r="T77" s="18" t="n">
-        <v>-31.95</v>
-      </c>
-      <c r="U77" s="34" t="n">
-        <v>-646.05</v>
-      </c>
-      <c r="V77" s="18" t="n">
-        <v>-422.59</v>
-      </c>
-      <c r="W77" s="18" t="n">
-        <v>-648.27</v>
-      </c>
-      <c r="X77" s="18" t="n">
-        <v>-389.91</v>
-      </c>
-      <c r="Y77" s="18" t="n">
-        <v>192.09</v>
-      </c>
-      <c r="Z77" s="34" t="n">
-        <v>-1268.68</v>
-      </c>
-      <c r="AA77" s="18" t="n">
-        <v>-189.75</v>
-      </c>
+      <c r="K77" s="9" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="U77" s="9" t="n"/>
+      <c r="Z77" s="9" t="n"/>
       <c r="AB77" s="19" t="n">
-        <v>-526.88</v>
+        <v>197.03</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -16975,78 +16767,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>-4511.4</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>21693.73</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>-4321.42</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-3187.64</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>3453.97</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>17638.64</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>-2001.56</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>-4935.14</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>-8376.209999999999</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>-4173.14</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>-19486.05</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>-1645.65</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>1090.63</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>-661.97</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>-16134.44</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>-17351.43</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>-24517</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>-3436.67</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>-4204.69</v>
-      </c>
-      <c r="Y78" s="18" t="n">
-        <v>2914.7</v>
-      </c>
-      <c r="Z78" s="34" t="n">
-        <v>-29243.66</v>
-      </c>
-      <c r="AA78" s="18" t="n">
-        <v>-29771.08</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
+      <c r="Z78" s="9" t="n"/>
       <c r="AB78" s="19" t="n">
-        <v>-1704.77</v>
+        <v>-106.27</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -17068,78 +16798,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>1461.21</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>872.5</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>4046.33</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>1166.19</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>829.17</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>6914.19</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>615.67</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>4180.02</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>7424.12</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>5329.47</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>17549.28</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>361.59</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>725.09</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>768.98</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>5507.34</v>
-      </c>
-      <c r="U79" s="34" t="n">
-        <v>7363</v>
-      </c>
-      <c r="V79" s="18" t="n">
-        <v>7279.15</v>
-      </c>
-      <c r="W79" s="18" t="n">
-        <v>7614.47</v>
-      </c>
-      <c r="X79" s="18" t="n">
-        <v>11619.69</v>
-      </c>
-      <c r="Y79" s="18" t="n">
-        <v>10652.03</v>
-      </c>
-      <c r="Z79" s="34" t="n">
-        <v>37165.34</v>
-      </c>
-      <c r="AA79" s="18" t="n">
-        <v>20972.69</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
+      <c r="Z79" s="9" t="n"/>
       <c r="AB79" s="19" t="n">
-        <v>11426.04</v>
+        <v>-22.96</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -17161,78 +16829,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>1461.21</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>874.75</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>4046.33</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>1169.97</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>829.17</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>6920.22</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>637.27</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>4190.72</v>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>7424.12</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>5329.47</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>17581.58</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>361.59</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>725.09</v>
-      </c>
-      <c r="S80" s="18" t="n">
-        <v>788.8099999999999</v>
-      </c>
-      <c r="T80" s="18" t="n">
-        <v>5546.16</v>
-      </c>
-      <c r="U80" s="34" t="n">
-        <v>7421.65</v>
-      </c>
-      <c r="V80" s="18" t="n">
-        <v>7303.32</v>
-      </c>
-      <c r="W80" s="18" t="n">
-        <v>8329.51</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>10880.48</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>10652.03</v>
-      </c>
-      <c r="Z80" s="34" t="n">
-        <v>37165.34</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>20972.69</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
+      <c r="U80" s="9" t="n"/>
+      <c r="Z80" s="9" t="n"/>
       <c r="AB80" s="19" t="n">
-        <v>11426.04</v>
+        <v>13231.27</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -17254,55 +16860,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>0</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>38.82</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
-      <c r="V81" s="18" t="n">
-        <v>24.17</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>715.04</v>
-      </c>
       <c r="Z81" s="9" t="n"/>
-      <c r="AB81" s="5" t="n"/>
+      <c r="AB81" s="19" t="n">
+        <v>12408.05</v>
+      </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -17323,78 +16891,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-7210.76</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-13505.41</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>6196.49</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>4480.16</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-8195.42</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-11024.18</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>9567.15</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>5133.36</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>11018.27</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-4436</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>21282.78</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>4898.6</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-2853.68</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-6130.98</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>19194.24</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>15108.18</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>17897.1</v>
-      </c>
-      <c r="W82" s="18" t="n">
-        <v>1109.67</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>5805.41</v>
-      </c>
-      <c r="Y82" s="18" t="n">
-        <v>26479.46</v>
-      </c>
-      <c r="Z82" s="34" t="n">
-        <v>51291.64</v>
-      </c>
-      <c r="AA82" s="18" t="n">
-        <v>8785.690000000001</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
+      <c r="Z82" s="9" t="n"/>
       <c r="AB82" s="19" t="n">
-        <v>1349.6</v>
+        <v>-995.34</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -17416,78 +16922,78 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>26394.16</v>
+        <v>23553.35</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>20607.81</v>
+        <v>-6348.39</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>51739.57</v>
+        <v>-10704.54</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>40208.48</v>
+        <v>219.35</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>43501.19</v>
+        <v>7160.8</v>
       </c>
       <c r="K83" s="34" t="n">
-        <v>156057.05</v>
+        <v>-9672.780000000001</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>48530.94</v>
+        <v>-12823.7</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>71058.95</v>
+        <v>1188.99</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>67856.27</v>
+        <v>-1097.21</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>19120.18</v>
+        <v>17935.62</v>
       </c>
       <c r="P83" s="34" t="n">
-        <v>206566.34</v>
+        <v>5203.7</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>59203.05</v>
+        <v>-6817.31</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>40073.7</v>
+        <v>-141.65</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>44038.24</v>
+        <v>7484.89</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>53570.48</v>
+        <v>-4376.7</v>
       </c>
       <c r="U83" s="34" t="n">
-        <v>196885.47</v>
+        <v>-3850.77</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>54408.19</v>
+        <v>8809.92</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>44444.9</v>
+        <v>-4361.97</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>54854.28</v>
+        <v>-1827.95</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>38109.87</v>
+        <v>-5555.15</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>191817.24</v>
+        <v>-2935.15</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>31000.03</v>
+        <v>9937.16</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>23769.97</v>
+        <v>3266.37</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -17509,32 +17015,69 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0</v>
+        <v>1278.99</v>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="K84" s="9" t="n"/>
+      <c r="G84" s="18" t="n">
+        <v>1295.36</v>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>1319.42</v>
+      </c>
+      <c r="I84" s="18" t="n">
+        <v>1299.61</v>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>1311.88</v>
+      </c>
+      <c r="K84" s="34" t="n">
+        <v>5226.27</v>
+      </c>
+      <c r="L84" s="18" t="n">
+        <v>1306.27</v>
+      </c>
+      <c r="M84" s="18" t="n">
+        <v>1315.98</v>
+      </c>
       <c r="N84" s="18" t="n">
-        <v>7100</v>
+        <v>1248.51</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P84" s="9" t="n"/>
+        <v>1256.47</v>
+      </c>
+      <c r="P84" s="34" t="n">
+        <v>5127.23</v>
+      </c>
+      <c r="Q84" s="18" t="n">
+        <v>1098.99</v>
+      </c>
+      <c r="R84" s="18" t="n">
+        <v>1073.65</v>
+      </c>
+      <c r="S84" s="18" t="n">
+        <v>1092.27</v>
+      </c>
       <c r="T84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="9" t="n"/>
+        <v>1114.48</v>
+      </c>
+      <c r="U84" s="34" t="n">
+        <v>4379.39</v>
+      </c>
+      <c r="V84" s="18" t="n">
+        <v>851.96</v>
+      </c>
+      <c r="W84" s="18" t="n">
+        <v>866.21</v>
+      </c>
+      <c r="X84" s="18" t="n">
+        <v>843.39</v>
+      </c>
       <c r="Z84" s="9" t="n"/>
-      <c r="AA84" s="18" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB84" s="19" t="n">
-        <v>2125.22</v>
-      </c>
+      <c r="AB84" s="5" t="n"/>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -17555,79 +17098,69 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>32215.18</v>
+        <v>20.36</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>29636.97</v>
+        <v>19.59</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>45239.56</v>
+        <v>17.77</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>35208.48</v>
+        <v>17.86</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>51131.19</v>
+        <v>17.86</v>
       </c>
       <c r="K85" s="34" t="n">
-        <v>161216.2</v>
+        <v>73.08</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>38847.94</v>
+        <v>12.13</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>67597.95</v>
+        <v>12.41</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>60310.27</v>
+        <v>12.39</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>50418.3</v>
+        <v>10.21</v>
       </c>
       <c r="P85" s="34" t="n">
-        <v>217174.46</v>
+        <v>47.14</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>48165.2</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>42773.69</v>
+        <v>7.59</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>49588.25</v>
+        <v>8.02</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>34270.47</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="U85" s="34" t="n">
-        <v>174797.61</v>
+        <v>32.95</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>57608.19</v>
+        <v>7.49</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>42754.9</v>
+        <v>6.68</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>48894.28</v>
-      </c>
-      <c r="Y85" s="18" t="n">
-        <v>37809.87</v>
-      </c>
-      <c r="Z85" s="34" t="n">
-        <v>187067.24</v>
-      </c>
-      <c r="AA85" s="18" t="n">
-        <v>32300.03</v>
-      </c>
-      <c r="AB85" s="19" t="n">
-        <v>17469.97</v>
-      </c>
+        <v>7.57</v>
+      </c>
+      <c r="Z85" s="9" t="n"/>
+      <c r="AB85" s="5" t="n"/>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="11" t="n"/>
@@ -17648,55 +17181,79 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>1267.59</v>
+        <v>-11.17</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>2055.43</v>
+        <v>-1404.33</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>198.31</v>
+        <v>-1727.34</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>178.56</v>
+        <v>-1500.5</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>0</v>
+        <v>-17.19</v>
       </c>
       <c r="K86" s="34" t="n">
-        <v>2432.3</v>
+        <v>-4649.36</v>
+      </c>
+      <c r="L86" s="18" t="n">
+        <v>-1391.98</v>
+      </c>
+      <c r="M86" s="18" t="n">
+        <v>-1852.12</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>3500</v>
+        <v>-762.86</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="9" t="n"/>
+        <v>-238.98</v>
+      </c>
+      <c r="P86" s="34" t="n">
+        <v>-4245.94</v>
+      </c>
       <c r="Q86" s="18" t="n">
-        <v>6000</v>
+        <v>-11.53</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0</v>
+        <v>-210.94</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>0</v>
+        <v>-391.63</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>0</v>
+        <v>-31.95</v>
       </c>
       <c r="U86" s="34" t="n">
-        <v>6000</v>
+        <v>-646.05</v>
+      </c>
+      <c r="V86" s="18" t="n">
+        <v>-422.59</v>
+      </c>
+      <c r="W86" s="18" t="n">
+        <v>-648.27</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" s="9" t="n"/>
-      <c r="AB86" s="5" t="n"/>
+        <v>-389.91</v>
+      </c>
+      <c r="Y86" s="18" t="n">
+        <v>192.09</v>
+      </c>
+      <c r="Z86" s="34" t="n">
+        <v>-1268.68</v>
+      </c>
+      <c r="AA86" s="18" t="n">
+        <v>-189.75</v>
+      </c>
+      <c r="AB86" s="19" t="n">
+        <v>-526.88</v>
+      </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -17717,78 +17274,78 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>23662.07</v>
+        <v>-4511.4</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>1839.93</v>
+        <v>21693.73</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>-8829.469999999999</v>
+        <v>-4321.42</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>1511.88</v>
+        <v>-3187.64</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>2419.34</v>
+        <v>3453.97</v>
       </c>
       <c r="K87" s="34" t="n">
-        <v>-3058.32</v>
+        <v>17638.64</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>-5258.1</v>
+        <v>-2001.56</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>1387.19</v>
+        <v>-4935.14</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>1544.87</v>
+        <v>-8376.209999999999</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>9326.469999999999</v>
+        <v>-4173.14</v>
       </c>
       <c r="P87" s="34" t="n">
-        <v>7000.43</v>
+        <v>-19486.05</v>
       </c>
       <c r="Q87" s="18" t="n">
-        <v>-3564.36</v>
+        <v>-1645.65</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>-1904.71</v>
+        <v>1090.63</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>691.95</v>
+        <v>-661.97</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>-1316.89</v>
+        <v>-16134.44</v>
       </c>
       <c r="U87" s="34" t="n">
-        <v>-6094.01</v>
+        <v>-17351.43</v>
       </c>
       <c r="V87" s="18" t="n">
-        <v>2190.02</v>
+        <v>-24517</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>-6688.97</v>
+        <v>-3436.67</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>-227.24</v>
+        <v>-4204.69</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>23839.03</v>
+        <v>2914.7</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>19112.84</v>
+        <v>-29243.66</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>-11048.23</v>
+        <v>-29771.08</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>2911.2</v>
+        <v>-1704.77</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -17810,78 +17367,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>11830.87</v>
+        <v>1461.21</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>15481.2</v>
+        <v>872.5</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-8674.139999999999</v>
+        <v>4046.33</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>1601.97</v>
+        <v>1166.19</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>2215.61</v>
+        <v>829.17</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>10624.64</v>
+        <v>6914.19</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>5378.3</v>
+        <v>615.67</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>1382.24</v>
+        <v>4180.02</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>1544.11</v>
+        <v>7424.12</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>9320.629999999999</v>
+        <v>5329.47</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>17625.28</v>
+        <v>17549.28</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>14072.42</v>
+        <v>361.59</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>-1917.37</v>
+        <v>725.09</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>674.37</v>
+        <v>768.98</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>-1284.23</v>
+        <v>5507.34</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>11545.19</v>
+        <v>7363</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>13828.71</v>
+        <v>7279.15</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>-6694.46</v>
+        <v>7614.47</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>-225.16</v>
+        <v>11619.69</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>23761.75</v>
+        <v>10652.03</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>30670.84</v>
+        <v>37165.34</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>19668.35</v>
+        <v>20972.69</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>2888.52</v>
+        <v>11426.04</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -17903,75 +17460,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>1461.21</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>25.36</v>
+        <v>874.75</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>2.5</v>
+        <v>4046.33</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>23</v>
+        <v>1169.97</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>2629.27</v>
+        <v>829.17</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>2680.13</v>
+        <v>6920.22</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>75.2</v>
+        <v>637.27</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>165</v>
+        <v>4190.72</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>3.2</v>
+        <v>7424.12</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>0</v>
+        <v>5329.47</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>243.4</v>
+        <v>17581.58</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>1.2</v>
+        <v>361.59</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>51.82</v>
+        <v>725.09</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>21.53</v>
+        <v>788.8099999999999</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>103.6</v>
+        <v>5546.16</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>178.15</v>
+        <v>7421.65</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>18.29</v>
+        <v>7303.32</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>40</v>
+        <v>8329.51</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>173.74</v>
+        <v>10880.48</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>9.65</v>
+        <v>10652.03</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>241.68</v>
+        <v>37165.34</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>114.1</v>
+        <v>20972.69</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>26.2</v>
+        <v>11426.04</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17993,30 +17553,53 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>2321.4</v>
+        <v>2.25</v>
       </c>
       <c r="H90" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="J90" s="18" t="n">
         <v>0</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>2321.4</v>
-      </c>
-      <c r="P90" s="9" t="n"/>
+        <v>6.03</v>
+      </c>
+      <c r="L90" s="18" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M90" s="18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N90" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="34" t="n">
+        <v>32.3</v>
+      </c>
       <c r="T90" s="18" t="n">
-        <v>0</v>
+        <v>38.82</v>
       </c>
       <c r="U90" s="9" t="n"/>
+      <c r="V90" s="18" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="W90" s="18" t="n">
+        <v>715.04</v>
+      </c>
       <c r="Z90" s="9" t="n"/>
       <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
@@ -18039,18 +17622,79 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>-7210.76</v>
       </c>
       <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>-13505.41</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>6196.49</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>4480.16</v>
+      </c>
       <c r="J91" s="18" t="n">
-        <v>1466.52</v>
-      </c>
-      <c r="K91" s="9" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="U91" s="9" t="n"/>
-      <c r="Z91" s="9" t="n"/>
-      <c r="AB91" s="5" t="n"/>
+        <v>-8195.42</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>-11024.18</v>
+      </c>
+      <c r="L91" s="18" t="n">
+        <v>9567.15</v>
+      </c>
+      <c r="M91" s="18" t="n">
+        <v>5133.36</v>
+      </c>
+      <c r="N91" s="18" t="n">
+        <v>11018.27</v>
+      </c>
+      <c r="O91" s="18" t="n">
+        <v>-4436</v>
+      </c>
+      <c r="P91" s="34" t="n">
+        <v>21282.78</v>
+      </c>
+      <c r="Q91" s="18" t="n">
+        <v>4898.6</v>
+      </c>
+      <c r="R91" s="18" t="n">
+        <v>-2853.68</v>
+      </c>
+      <c r="S91" s="18" t="n">
+        <v>-6130.98</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>19194.24</v>
+      </c>
+      <c r="U91" s="34" t="n">
+        <v>15108.18</v>
+      </c>
+      <c r="V91" s="18" t="n">
+        <v>17897.1</v>
+      </c>
+      <c r="W91" s="18" t="n">
+        <v>1109.67</v>
+      </c>
+      <c r="X91" s="18" t="n">
+        <v>5805.41</v>
+      </c>
+      <c r="Y91" s="18" t="n">
+        <v>26479.46</v>
+      </c>
+      <c r="Z91" s="34" t="n">
+        <v>51291.64</v>
+      </c>
+      <c r="AA91" s="18" t="n">
+        <v>8785.690000000001</v>
+      </c>
+      <c r="AB91" s="19" t="n">
+        <v>1349.6</v>
+      </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -18071,21 +17715,79 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>26394.16</v>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="K92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>20607.81</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>51739.57</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>40208.48</v>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>43501.19</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>156057.05</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>48530.94</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>71058.95</v>
+      </c>
       <c r="N92" s="18" t="n">
-        <v>0</v>
+        <v>67856.27</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="9" t="n"/>
-      <c r="U92" s="9" t="n"/>
-      <c r="Z92" s="9" t="n"/>
-      <c r="AB92" s="5" t="n"/>
+        <v>19120.18</v>
+      </c>
+      <c r="P92" s="34" t="n">
+        <v>206566.34</v>
+      </c>
+      <c r="Q92" s="18" t="n">
+        <v>59203.05</v>
+      </c>
+      <c r="R92" s="18" t="n">
+        <v>40073.7</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>44038.24</v>
+      </c>
+      <c r="T92" s="18" t="n">
+        <v>53570.48</v>
+      </c>
+      <c r="U92" s="34" t="n">
+        <v>196885.47</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>54408.19</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>44444.9</v>
+      </c>
+      <c r="X92" s="18" t="n">
+        <v>54854.28</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>38109.87</v>
+      </c>
+      <c r="Z92" s="34" t="n">
+        <v>191817.24</v>
+      </c>
+      <c r="AA92" s="18" t="n">
+        <v>31000.03</v>
+      </c>
+      <c r="AB92" s="19" t="n">
+        <v>23769.97</v>
+      </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -18106,50 +17808,31 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="K93" s="9" t="n"/>
+      <c r="N93" s="18" t="n">
+        <v>7100</v>
+      </c>
       <c r="O93" s="18" t="n">
-        <v>137.58</v>
+        <v>2000</v>
       </c>
       <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="18" t="n">
-        <v>114.59</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="S93" s="18" t="n">
-        <v>83.2</v>
-      </c>
       <c r="T93" s="18" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>351.79</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>89.61</v>
-      </c>
-      <c r="X93" s="18" t="n">
-        <v>231.57</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="Z93" s="34" t="n">
-        <v>461.08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U93" s="9" t="n"/>
+      <c r="Z93" s="9" t="n"/>
       <c r="AA93" s="18" t="n">
-        <v>70.14</v>
+        <v>10000</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>147.15</v>
+        <v>2125.22</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -18171,41 +17854,79 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>32215.18</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>29636.97</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>45239.56</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>35208.48</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>51131.19</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>161216.2</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>38847.94</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>67597.95</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>60310.27</v>
+      </c>
       <c r="O94" s="18" t="n">
-        <v>138.01</v>
-      </c>
-      <c r="P94" s="9" t="n"/>
+        <v>50418.3</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>217174.46</v>
+      </c>
       <c r="Q94" s="18" t="n">
-        <v>139.25</v>
+        <v>48165.2</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>153.69</v>
+        <v>42773.69</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>180.98</v>
+        <v>49588.25</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>180.9</v>
+        <v>34270.47</v>
       </c>
       <c r="U94" s="34" t="n">
-        <v>654.8200000000001</v>
+        <v>174797.61</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>191.56</v>
+        <v>57608.19</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>197.24</v>
+        <v>42754.9</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>187.01</v>
-      </c>
-      <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+        <v>48894.28</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>37809.87</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>187067.24</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>32300.03</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>17469.97</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -18219,6 +17940,584 @@
       <c r="AM94" s="10" t="n"/>
       <c r="AN94" s="10" t="n"/>
       <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>1267.59</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>2055.43</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>198.31</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>178.56</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>2432.3</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="O95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="9" t="n"/>
+      <c r="Q95" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="X95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="9" t="n"/>
+      <c r="AB95" s="5" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>23662.07</v>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>1839.93</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>-8829.469999999999</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>1511.88</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>2419.34</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>-3058.32</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>-5258.1</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>1387.19</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>1544.87</v>
+      </c>
+      <c r="O96" s="18" t="n">
+        <v>9326.469999999999</v>
+      </c>
+      <c r="P96" s="34" t="n">
+        <v>7000.43</v>
+      </c>
+      <c r="Q96" s="18" t="n">
+        <v>-3564.36</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>-1904.71</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>691.95</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>-1316.89</v>
+      </c>
+      <c r="U96" s="34" t="n">
+        <v>-6094.01</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>2190.02</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>-6688.97</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>-227.24</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>23839.03</v>
+      </c>
+      <c r="Z96" s="34" t="n">
+        <v>19112.84</v>
+      </c>
+      <c r="AA96" s="18" t="n">
+        <v>-11048.23</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>2911.2</v>
+      </c>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>11830.87</v>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>15481.2</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>-8674.139999999999</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>1601.97</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>2215.61</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>10624.64</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>5378.3</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>1382.24</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>1544.11</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>9320.629999999999</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>17625.28</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>14072.42</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>-1917.37</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>674.37</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>-1284.23</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>11545.19</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>13828.71</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>-6694.46</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>-225.16</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>23761.75</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>30670.84</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>19668.35</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>2888.52</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>2629.27</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>2680.13</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>165</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>173.74</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>241.68</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>2321.4</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>2321.4</v>
+      </c>
+      <c r="P99" s="9" t="n"/>
+      <c r="T99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="9" t="n"/>
+      <c r="Z99" s="9" t="n"/>
+      <c r="AB99" s="5" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="J100" s="18" t="n">
+        <v>1466.52</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
+      <c r="P100" s="9" t="n"/>
+      <c r="U100" s="9" t="n"/>
+      <c r="Z100" s="9" t="n"/>
+      <c r="AB100" s="5" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="N101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="9" t="n"/>
+      <c r="U101" s="9" t="n"/>
+      <c r="Z101" s="9" t="n"/>
+      <c r="AB101" s="5" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+      <c r="O102" s="18" t="n">
+        <v>137.58</v>
+      </c>
+      <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="18" t="n">
+        <v>114.59</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>351.79</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>231.57</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>461.08</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>147.15</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="O103" s="18" t="n">
+        <v>138.01</v>
+      </c>
+      <c r="P103" s="9" t="n"/>
+      <c r="Q103" s="18" t="n">
+        <v>139.25</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>654.8200000000001</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>191.56</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>197.24</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>187.01</v>
+      </c>
+      <c r="Z103" s="9" t="n"/>
+      <c r="AB103" s="5" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18479,7 +18778,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28697,10 +28996,10 @@
         <v/>
       </c>
       <c r="AF18" s="20" t="n">
-        <v>40.78</v>
+        <v>41.26</v>
       </c>
       <c r="AG18" s="20" t="n">
-        <v>40.55</v>
+        <v>42.36</v>
       </c>
       <c r="AH18" s="20">
         <f>IFERROR(AC18*(1+변수!AH30),"")</f>
@@ -29516,9 +29815,12 @@
         <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(X$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="Y23" s="18" t="n"/>
+      <c r="Y23" s="18">
+        <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(Y$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="Z23" s="34">
-        <f>Y23</f>
+        <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(Z$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="AA23" s="18" t="n"/>
@@ -29647,9 +29949,12 @@
         <f>IFERROR(VLOOKUP($D24,BS연결,MATCH(X$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
-      <c r="Y24" s="18" t="n"/>
+      <c r="Y24" s="18">
+        <f>IFERROR(VLOOKUP($D24,BS연결,MATCH(Y$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
       <c r="Z24" s="34">
-        <f>Y24</f>
+        <f>IFERROR(VLOOKUP($D24,BS연결,MATCH(Z$1,BS연결H,0),0)/100,"")</f>
         <v/>
       </c>
       <c r="AA24" s="18" t="n"/>
@@ -30911,13 +31216,13 @@
         <v/>
       </c>
       <c r="AF33" s="20" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="AG33" s="20" t="n">
-        <v>14.23</v>
+        <v>13.98</v>
       </c>
       <c r="AH33" s="20" t="n">
-        <v>14.07</v>
+        <v>13.46</v>
       </c>
       <c r="AI33" s="20">
         <f>IFERROR(AD33*(1+변수!AI42),"")</f>
@@ -39383,7 +39688,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>160.6</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="30">
@@ -39403,7 +39708,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.23</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="32">
@@ -39423,7 +39728,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0281</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="34">
@@ -39433,7 +39738,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="35">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66101억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68341억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72257억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76505억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81467억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86550억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91777억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95826억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66101억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68341억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72257억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76505억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81467억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86550억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91777억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95826억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 20.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
+          <t>· 세율 20.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2340</v>
+        <v>2395</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2335</v>
+        <v>2355</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.319619043</v>
+        <v>0.319301438</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.257788501</v>
+        <v>0.257453871</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.141115525</v>
+        <v>0.140828388</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169902688</v>
+        <v>0.169636237</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232461921</v>
+        <v>0.23250642</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266444962</v>
+        <v>0.266549132</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.270143323</v>
+        <v>0.270253264</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252559761</v>
+        <v>0.252656914</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036881253</v>
+        <v>0.036890132</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036880612</v>
+        <v>0.036890426</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036884429</v>
+        <v>0.036883226</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036886301</v>
+        <v>0.036884799</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036880673</v>
+        <v>0.036888219</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036885318</v>
+        <v>0.036883344</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036881423</v>
+        <v>0.036887513</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036888</v>
+        <v>0.036885635</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005481506</v>
+        <v>-0.005075703</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.001989903</v>
+        <v>0.002427017</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.000879887</v>
+        <v>-0.000425264</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.000752976</v>
+        <v>0.009705910999999999</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.010638736</v>
+        <v>0.00196523</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.009524005</v>
+        <v>-0.007847702999999999</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.00760209</v>
+        <v>0.002963559</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.004709098</v>
+        <v>-0.001987898</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.000465885</v>
+        <v>0.011127792</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.007979569000000001</v>
+        <v>0.000758174</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.002568267</v>
+        <v>0.003209319</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007534123</v>
+        <v>-0.006864113</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.003317425</v>
+        <v>0.003995241</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.008644044</v>
+        <v>0.00205383</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.000623404</v>
+        <v>-0.00302999</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.00941407</v>
+        <v>0.007058651</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.011469371</v>
+        <v>-0.000600262</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.001653641</v>
+        <v>-0.000563825</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.005688416</v>
+        <v>-0.003299858</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.005332693</v>
+        <v>0.00256551</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8902,26 +8902,26 @@
         <v>0.05773276</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054182606</v>
+        <v>0.054195273</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050646752</v>
+        <v>0.050646144</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047399029</v>
+        <v>0.047404205</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044336831</v>
+        <v>0.044341564</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041555359</v>
+        <v>0.04155449</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.038998976</v>
+        <v>0.039003212</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.03688782</v>
+        <v>0.036886929</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9027,29 +9027,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>-1.208017942</v>
+        <v>-1.208158116</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.765498652</v>
+        <v>5.761616162</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.839541833</v>
+        <v>0.839557813</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.448806108</v>
+        <v>0.448811651</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.303535391</v>
+        <v>0.303501364</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.227895642</v>
+        <v>0.22790471</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181395783</v>
+        <v>0.18140219</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.150915056</v>
+        <v>0.150900144</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2340</v>
+        <v>2395</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094510293200249</v>
+        <v>0.2094302094302094</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949365839214331</v>
+        <v>0.07949349244207167</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.3999802722430459</v>
+        <v>0.400009865824783</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418309309525126</v>
+        <v>0.01418211991465084</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682562419236337</v>
+        <v>0.02682553656290636</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34140,7 +34140,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39529,7 +39529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41757,7 +41757,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.06</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="32">
@@ -41767,7 +41767,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="33">
@@ -41807,7 +41807,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.6</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 20.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
+          <t>· 세율 20.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2395</v>
+        <v>2345</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6493,7 +6493,7 @@
         <v>2870</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2405</v>
+        <v>2410</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2355</v>
+        <v>2351.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.319301438</v>
+        <v>0.319029205</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.257453871</v>
+        <v>0.257035584</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.140828388</v>
+        <v>0.140481432</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169636237</v>
+        <v>0.169311863</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.23250642</v>
+        <v>0.232451212</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266549132</v>
+        <v>0.266693287</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.270253264</v>
+        <v>0.270377442</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252656914</v>
+        <v>0.252776539</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036890132</v>
+        <v>0.03688628</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036890426</v>
+        <v>0.036880518</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036883226</v>
+        <v>0.036883956</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036884799</v>
+        <v>0.036885124</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036888219</v>
+        <v>0.036888182</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036883344</v>
+        <v>0.036882662</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036887513</v>
+        <v>0.03688687</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036885635</v>
+        <v>0.036884436</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005075703</v>
+        <v>-0.005637848</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.002427017</v>
+        <v>0.001864303</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.000425264</v>
+        <v>0.001123739</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.009705910999999999</v>
+        <v>-0.006653433</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.00196523</v>
+        <v>0.003430525</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.007847702999999999</v>
+        <v>-0.006411211</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.002963559</v>
+        <v>0.004333215</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.001987898</v>
+        <v>-0.00068705</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.011127792</v>
+        <v>0.002384663</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.000758174</v>
+        <v>0.001958988</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.003209319</v>
+        <v>0.002345886</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.006864113</v>
+        <v>-0.007749695</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.003995241</v>
+        <v>-4.6491e-05</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.00205383</v>
+        <v>0.004824513</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.00302999</v>
+        <v>-0.007179511</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.007058651</v>
+        <v>0.002842339</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.000600262</v>
+        <v>-0.004909657</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.000563825</v>
+        <v>0.005031161</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.003299858</v>
+        <v>0.002206756</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.00256551</v>
+        <v>-0.002003179</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.05773276</v>
+        <v>0.057739459</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054195273</v>
+        <v>0.054194929</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050646144</v>
+        <v>0.050651847</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047404205</v>
+        <v>0.047409381</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044341564</v>
+        <v>0.044346297</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04155449</v>
+        <v>0.041558849</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039003212</v>
+        <v>0.039002233</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036886929</v>
+        <v>0.036890868</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9030,26 +9030,26 @@
         <v>-1.208158116</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.761616162</v>
+        <v>5.762962963</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.839557813</v>
+        <v>0.83939062</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.448811651</v>
+        <v>0.448817193</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.303501364</v>
+        <v>0.303504708</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.22790471</v>
+        <v>0.227878579</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.18140219</v>
+        <v>0.181408595</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.150900144</v>
+        <v>0.150904995</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2395</v>
+        <v>2345</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,315원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,330원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094302094302094</v>
+        <v>0.2094565599032497</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949349244207167</v>
+        <v>0.07949477226342382</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.400009865824783</v>
+        <v>0.3999703908409001</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418211991465084</v>
+        <v>0.01418107371011599</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682553656290636</v>
+        <v>0.02682544629119341</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34140,7 +34140,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39529,7 +39529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41757,7 +41757,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.56</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="32">
@@ -41767,7 +41767,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="33">
@@ -41807,7 +41807,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.68</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,7 +669,7 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
@@ -687,25 +687,25 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
@@ -1776,7 +1776,7 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1794,25 +1794,25 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2345</v>
+        <v>2325</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2351.2</v>
+        <v>2346</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.319029205</v>
+        <v>0.318862841</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.257035584</v>
+        <v>0.257021642</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.140481432</v>
+        <v>0.140469468</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169311863</v>
+        <v>0.169300278</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232451212</v>
+        <v>0.232606676</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266693287</v>
+        <v>0.266696245</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.270377442</v>
+        <v>0.270390768</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252776539</v>
+        <v>0.252788951</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,16 +7148,16 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.03688628</v>
+        <v>0.036890933</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036880518</v>
+        <v>0.036880927</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036883956</v>
+        <v>0.036884343</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036885124</v>
+        <v>0.03688549</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
@@ -7167,7 +7167,7 @@
         <v>0.036888182</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036882662</v>
+        <v>0.036882985</v>
       </c>
       <c r="AM23" s="24" t="n">
         <v>0.03688687</v>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005637848</v>
+        <v>-0.005642528</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.001864303</v>
+        <v>0.001862595</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.001123739</v>
+        <v>0.001125046</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.006653433</v>
+        <v>0.003350726</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.003430525</v>
+        <v>-0.006562292</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.006411211</v>
+        <v>0.003571223</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.004333215</v>
+        <v>0.004346075</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.00068705</v>
+        <v>-0.010671364</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.002384663</v>
+        <v>0.002374977</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.001958988</v>
+        <v>0.001951983</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.002345886</v>
+        <v>0.002344014</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007749695</v>
+        <v>-0.007750378</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-4.6491e-05</v>
+        <v>-4.5968e-05</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.004824513</v>
+        <v>0.004826176</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.007179511</v>
+        <v>-0.007176637</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.002842339</v>
+        <v>0.002835312</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.004909657</v>
+        <v>0.005095486</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.005031161</v>
+        <v>-0.004962564</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.002206756</v>
+        <v>0.002202881</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002003179</v>
+        <v>-0.00200598</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8902,10 +8902,10 @@
         <v>0.057739459</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054194929</v>
+        <v>0.054201263</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050651847</v>
+        <v>0.050645535</v>
       </c>
       <c r="AI35" s="24" t="n">
         <v>0.047409381</v>
@@ -9033,23 +9033,23 @@
         <v>5.762962963</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.83939062</v>
+        <v>0.839490192</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.448817193</v>
+        <v>0.448738768</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
         <v>0.303504708</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.227878579</v>
+        <v>0.227907243</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181408595</v>
+        <v>0.181404361</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.150904995</v>
+        <v>0.150902013</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2345</v>
+        <v>2325</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,330원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,375원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949477226342382</v>
+        <v>0.07949496226139367</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418107371011599</v>
+        <v>0.01418090039023007</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682544629119341</v>
+        <v>0.02682543421401418</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39529,7 +39529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41737,7 +41737,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>111.1</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
@@ -41757,7 +41757,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.11</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="32">
@@ -41807,7 +41807,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.61</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65394억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 65950억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1770,55 +1770,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65394억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 65950억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2136,13 +2136,13 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 71억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 72억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -15억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -14억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2154,13 +2154,13 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -185억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -184억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -268억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -267억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2196,13 +2196,13 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 71억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 72억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -15억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -14억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2214,13 +2214,13 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -185억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -184억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -268억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -267억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 20.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
+          <t>· 세율 20.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
         </is>
       </c>
     </row>
@@ -6830,33 +6830,33 @@
         <v>0.492327593</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.600798767</v>
+        <v>0.61441075</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.318862841</v>
+        <v>0.333457552</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.257021642</v>
+        <v>0.261162681</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.140469468</v>
+        <v>0.138184342</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169300278</v>
+        <v>0.153215246</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232606676</v>
+        <v>0.210337084</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266696245</v>
+        <v>0.252763897</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.270390768</v>
+        <v>0.264059117</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252788951</v>
+        <v>0.253018169</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7141,39 +7141,39 @@
         <v>0.03688505</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.036886006</v>
+        <v>0.036885152</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036890933</v>
+        <v>0.03688413</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036880927</v>
+        <v>0.03688144</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036884343</v>
+        <v>0.036884815</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.03688549</v>
+        <v>0.036885409</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036888182</v>
+        <v>0.036883979</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036882985</v>
+        <v>0.03688832</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.03688687</v>
+        <v>0.036888279</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036884436</v>
+        <v>0.036885995</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005642528</v>
+        <v>-0.004631838</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.001862595</v>
+        <v>0.006271214</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.001125046</v>
+        <v>-0.000701307</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.003350726</v>
+        <v>-0.007477934</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.006562292</v>
+        <v>0.000525206</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.003571223</v>
+        <v>-0.002284973</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.004346075</v>
+        <v>0.006870352</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.010671364</v>
+        <v>-0.00252764</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.002374977</v>
+        <v>0.007736861</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.001951983</v>
+        <v>0.001925668</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.002344014</v>
+        <v>0.001306224</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007750378</v>
+        <v>-0.003503837</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-4.5968e-05</v>
+        <v>-0.000302705</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.004826176</v>
+        <v>-0.011063612</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.007176637</v>
+        <v>3.697e-06</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.002835312</v>
+        <v>-0.001274413</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.005095486</v>
+        <v>0.002196635</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.004962564</v>
+        <v>-0.007764504</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.002202881</v>
+        <v>0.00212752</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.00200598</v>
+        <v>-0.000362513</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8895,33 +8895,33 @@
         <v>0.06574308800000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.061292685</v>
+        <v>0.061136272</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.057739459</v>
+        <v>0.057560368</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054201263</v>
+        <v>0.054161414</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050645535</v>
+        <v>0.050699553</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047409381</v>
+        <v>0.047515272</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044346297</v>
+        <v>0.044475387</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041558849</v>
+        <v>0.041698034</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039002233</v>
+        <v>0.039125547</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036890868</v>
+        <v>0.036976219</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9023,33 +9023,33 @@
         <v>-0.355125494</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>-0.547191368</v>
+        <v>-0.545858458</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>-1.208158116</v>
+        <v>-1.200698812</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.762962963</v>
+        <v>5.953342618</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.839490192</v>
+        <v>0.844867301</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.448738768</v>
+        <v>0.450898431</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.303504708</v>
+        <v>0.304785423</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.227907243</v>
+        <v>0.22868695</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181404361</v>
+        <v>0.181945482</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.150902013</v>
+        <v>0.151192639</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094565599032497</v>
+        <v>0.2094351431700829</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949496226139367</v>
+        <v>0.07949468769166848</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.3999703908409001</v>
+        <v>0.3998812527831379</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418090039023007</v>
+        <v>0.01418495436989992</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682543421401418</v>
+        <v>0.02682420084031387</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12982,58 +12982,58 @@
         <v>1220.25</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>370.78</v>
+        <v>1225.99</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>384.94</v>
+        <v>1195.39</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>366.59</v>
+        <v>1091.02</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>383.35</v>
+        <v>1155.82</v>
       </c>
       <c r="K28" s="37" t="n">
-        <v>383.35</v>
+        <v>1155.82</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>391.6</v>
+        <v>1135.56</v>
       </c>
       <c r="M28" s="18" t="n">
-        <v>440.86</v>
+        <v>1150.76</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>517.5</v>
+        <v>1138.43</v>
       </c>
       <c r="O28" s="18" t="n">
-        <v>477.32</v>
+        <v>1000.41</v>
       </c>
       <c r="P28" s="37" t="n">
-        <v>477.32</v>
+        <v>1000.41</v>
       </c>
       <c r="Q28" s="18" t="n">
-        <v>428.91</v>
+        <v>861.17</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>594.49</v>
+        <v>1153.8</v>
       </c>
       <c r="S28" s="18" t="n">
-        <v>666.15</v>
+        <v>1167.26</v>
       </c>
       <c r="T28" s="18" t="n">
-        <v>641.51</v>
+        <v>1126.03</v>
       </c>
       <c r="U28" s="37" t="n">
-        <v>641.51</v>
+        <v>1126.03</v>
       </c>
       <c r="V28" s="18" t="n">
-        <v>1020.1</v>
+        <v>1060.81</v>
       </c>
       <c r="W28" s="18" t="n">
-        <v>586.89</v>
+        <v>972.14</v>
       </c>
       <c r="X28" s="18" t="n">
-        <v>481.46</v>
+        <v>800.16</v>
       </c>
       <c r="Y28" s="18" t="n">
         <v>729.78</v>
@@ -13728,9 +13728,60 @@
       <c r="F36" s="37" t="n">
         <v>860.42</v>
       </c>
-      <c r="K36" s="9" t="n"/>
-      <c r="P36" s="9" t="n"/>
-      <c r="U36" s="9" t="n"/>
+      <c r="G36" s="18" t="n">
+        <v>855.21</v>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>810.45</v>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>724.4299999999999</v>
+      </c>
+      <c r="J36" s="18" t="n">
+        <v>772.47</v>
+      </c>
+      <c r="K36" s="37" t="n">
+        <v>772.47</v>
+      </c>
+      <c r="L36" s="18" t="n">
+        <v>743.96</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="N36" s="18" t="n">
+        <v>620.9299999999999</v>
+      </c>
+      <c r="O36" s="18" t="n">
+        <v>523.09</v>
+      </c>
+      <c r="P36" s="37" t="n">
+        <v>523.09</v>
+      </c>
+      <c r="Q36" s="18" t="n">
+        <v>432.26</v>
+      </c>
+      <c r="R36" s="18" t="n">
+        <v>559.3099999999999</v>
+      </c>
+      <c r="S36" s="18" t="n">
+        <v>501.11</v>
+      </c>
+      <c r="T36" s="18" t="n">
+        <v>484.52</v>
+      </c>
+      <c r="U36" s="37" t="n">
+        <v>484.52</v>
+      </c>
+      <c r="V36" s="18" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="W36" s="18" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="X36" s="18" t="n">
+        <v>318.7</v>
+      </c>
       <c r="Y36" s="18" t="n">
         <v>350.6</v>
       </c>
@@ -13773,58 +13824,58 @@
         <v>1410.42</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>556</v>
+        <v>1411.21</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>556</v>
+        <v>1366.45</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>506</v>
+        <v>1230.43</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>506</v>
+        <v>1278.47</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>506</v>
+        <v>1278.47</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>556</v>
+        <v>1299.96</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>576</v>
+        <v>1285.9</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>656</v>
+        <v>1276.93</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>736</v>
+        <v>1259.09</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>736</v>
+        <v>1259.09</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>776</v>
+        <v>1208.26</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>816</v>
+        <v>1375.31</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>876</v>
+        <v>1377.11</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>216</v>
+        <v>700.52</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>216</v>
+        <v>700.52</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>5011.66</v>
+        <v>5052.37</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>3998.45</v>
+        <v>4383.7</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>3992.45</v>
+        <v>4311.15</v>
       </c>
       <c r="Y37" s="18" t="n">
         <v>570.6</v>
@@ -19580,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21884,58 +21935,58 @@
         <v>1615.94</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>400.13</v>
+        <v>1518.44</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>404.33</v>
+        <v>1445.06</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>408.25</v>
+        <v>1345.09</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>412.28</v>
+        <v>1244.72</v>
       </c>
       <c r="K27" s="37" t="n">
-        <v>412.28</v>
+        <v>1244.72</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>300.01</v>
+        <v>773.71</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>308.07</v>
+        <v>721.89</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>303.22</v>
+        <v>645.9299999999999</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>294.76</v>
+        <v>569.37</v>
       </c>
       <c r="P27" s="37" t="n">
-        <v>294.76</v>
+        <v>569.37</v>
       </c>
       <c r="Q27" s="18" t="n">
-        <v>277.97</v>
+        <v>491.88</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>281.67</v>
+        <v>500.98</v>
       </c>
       <c r="S27" s="18" t="n">
-        <v>290.57</v>
+        <v>520.6799999999999</v>
       </c>
       <c r="T27" s="18" t="n">
-        <v>301.61</v>
+        <v>581.75</v>
       </c>
       <c r="U27" s="37" t="n">
-        <v>301.61</v>
+        <v>581.75</v>
       </c>
       <c r="V27" s="18" t="n">
-        <v>278.21</v>
+        <v>503.37</v>
       </c>
       <c r="W27" s="18" t="n">
-        <v>235.33</v>
+        <v>494.45</v>
       </c>
       <c r="X27" s="18" t="n">
-        <v>187.49</v>
+        <v>445.76</v>
       </c>
       <c r="Y27" s="18" t="n">
         <v>401.57</v>
@@ -22625,9 +22676,60 @@
       <c r="F35" s="37" t="n">
         <v>1219.73</v>
       </c>
-      <c r="K35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="U35" s="9" t="n"/>
+      <c r="G35" s="18" t="n">
+        <v>1118.31</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>1040.73</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>936.84</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>832.4400000000001</v>
+      </c>
+      <c r="K35" s="37" t="n">
+        <v>832.4400000000001</v>
+      </c>
+      <c r="L35" s="18" t="n">
+        <v>473.7</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <v>413.82</v>
+      </c>
+      <c r="N35" s="18" t="n">
+        <v>342.71</v>
+      </c>
+      <c r="O35" s="18" t="n">
+        <v>274.61</v>
+      </c>
+      <c r="P35" s="37" t="n">
+        <v>274.61</v>
+      </c>
+      <c r="Q35" s="18" t="n">
+        <v>213.91</v>
+      </c>
+      <c r="R35" s="18" t="n">
+        <v>219.31</v>
+      </c>
+      <c r="S35" s="18" t="n">
+        <v>230.11</v>
+      </c>
+      <c r="T35" s="18" t="n">
+        <v>280.14</v>
+      </c>
+      <c r="U35" s="37" t="n">
+        <v>280.14</v>
+      </c>
+      <c r="V35" s="18" t="n">
+        <v>225.16</v>
+      </c>
+      <c r="W35" s="18" t="n">
+        <v>259.12</v>
+      </c>
+      <c r="X35" s="18" t="n">
+        <v>258.27</v>
+      </c>
       <c r="Y35" s="18" t="n">
         <v>255.97</v>
       </c>
@@ -22670,58 +22772,58 @@
         <v>1423.73</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>210</v>
+        <v>1328.31</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>210</v>
+        <v>1250.73</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>160</v>
+        <v>1096.84</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>160</v>
+        <v>992.4400000000001</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>160</v>
+        <v>992.4400000000001</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>190</v>
+        <v>663.7</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>405</v>
+        <v>818.8200000000001</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>405</v>
+        <v>747.71</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>425</v>
+        <v>699.61</v>
       </c>
       <c r="P36" s="37" t="n">
-        <v>425</v>
+        <v>699.61</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>425</v>
+        <v>638.91</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>425</v>
+        <v>644.3099999999999</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>411</v>
+        <v>641.11</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>411</v>
+        <v>691.14</v>
       </c>
       <c r="U36" s="37" t="n">
-        <v>411</v>
+        <v>691.14</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>396</v>
+        <v>621.16</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>396</v>
+        <v>655.12</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>390</v>
+        <v>648.27</v>
       </c>
       <c r="Y36" s="18" t="n">
         <v>655.97</v>
@@ -41737,7 +41839,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30">
@@ -41757,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.95</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="32">
@@ -41777,7 +41879,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0195</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="34">
@@ -41807,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.58</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2325</v>
+        <v>2310</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.333457552</v>
+        <v>0.33341218</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.261162681</v>
+        <v>0.261553082</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138184342</v>
+        <v>0.138531298</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153215246</v>
+        <v>0.153525398</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210337084</v>
+        <v>0.21067317</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252763897</v>
+        <v>0.25265252</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.264059117</v>
+        <v>0.263926106</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.253018169</v>
+        <v>0.252900348</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.03688413</v>
+        <v>0.036885385</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.03688144</v>
+        <v>0.036881079</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036884815</v>
+        <v>0.036884083</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036885409</v>
+        <v>0.03688545</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036883979</v>
+        <v>0.036884363</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.03688832</v>
+        <v>0.036889007</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036888279</v>
+        <v>0.036889233</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036885995</v>
+        <v>0.036887494</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004631838</v>
+        <v>-0.004407448</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006271214</v>
+        <v>0.006491485</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.000701307</v>
+        <v>-0.000493777</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.007477934</v>
+        <v>-0.00937285</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.000525206</v>
+        <v>0.008658832999999999</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.002284973</v>
+        <v>-0.004120155</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.006870352</v>
+        <v>0.005041918</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.00252764</v>
+        <v>0.005681314</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.007736861</v>
+        <v>-0.004044162</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.001925668</v>
+        <v>0.01017811</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.001306224</v>
+        <v>0.004117307</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.003503837</v>
+        <v>-0.000565093</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.000302705</v>
+        <v>0.002644909</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.011063612</v>
+        <v>-0.004885395</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>3.697e-06</v>
+        <v>0.006383081</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.001274413</v>
+        <v>-0.004664342</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.002196635</v>
+        <v>-0.0009199120000000001</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.007764504</v>
+        <v>0.009419975000000001</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.00212752</v>
+        <v>-0.00038116</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000362513</v>
+        <v>0.007376719</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.057560368</v>
+        <v>0.057567068</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054161414</v>
+        <v>0.0541484</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050699553</v>
+        <v>0.050699858</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047515272</v>
+        <v>0.047504104</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044475387</v>
+        <v>0.044476116</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041698034</v>
+        <v>0.04169346</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039125547</v>
+        <v>0.039121314</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036976219</v>
+        <v>0.036977111</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9030,26 +9030,26 @@
         <v>-1.200698812</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.953342618</v>
+        <v>5.95264624</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.844867301</v>
+        <v>0.844851763</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.450898431</v>
+        <v>0.450947391</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.304785423</v>
+        <v>0.304770814</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.22868695</v>
+        <v>0.228706625</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181945482</v>
+        <v>0.181934882</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.151192639</v>
+        <v>0.151165087</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2325</v>
+        <v>2310</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,375원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,365원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094351431700829</v>
+        <v>0.2094251075479077</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949468769166848</v>
+        <v>0.07949453927547728</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.3998812527831379</v>
+        <v>0.4000494682166707</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418495436989992</v>
+        <v>0.01418576362903842</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682420084031387</v>
+        <v>0.02682426648205364</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.76</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="32">
@@ -41869,7 +41869,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.53</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.33341218</v>
+        <v>0.333351684</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.261553082</v>
+        <v>0.26139971</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138531298</v>
+        <v>0.13838773</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153525398</v>
+        <v>0.15339904</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.21067317</v>
+        <v>0.210603328</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.25265252</v>
+        <v>0.252694293</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263926106</v>
+        <v>0.26398041</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252900348</v>
+        <v>0.252947972</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036885385</v>
+        <v>0.036887059</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036881079</v>
+        <v>0.036885563</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036884083</v>
+        <v>0.036888735</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.03688545</v>
+        <v>0.036889491</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036884363</v>
+        <v>0.036888164</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036889007</v>
+        <v>0.036883438</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036889233</v>
+        <v>0.036883985</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036887494</v>
+        <v>0.036882184</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004407448</v>
+        <v>-0.004752091</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006491485</v>
+        <v>0.006136873</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.000493777</v>
+        <v>-0.0008438779999999999</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-0.00937285</v>
+        <v>0.000273465</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.008658832999999999</v>
+        <v>-0.001711853</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.004120155</v>
+        <v>0.005459849</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.005041918</v>
+        <v>0.004593767</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>0.005681314</v>
+        <v>-0.002701832</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.004044162</v>
+        <v>0.007540562</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.01017811</v>
+        <v>-0.008288373</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004117307</v>
+        <v>0.002698978</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.000565093</v>
+        <v>-0.002048252</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.002644909</v>
+        <v>0.001156982</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.004885395</v>
+        <v>-0.006408877</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.006383081</v>
+        <v>0.004763514</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.004664342</v>
+        <v>0.003593691</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.0009199120000000001</v>
+        <v>-0.002800504</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.009419975000000001</v>
+        <v>-0.005768987</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.00038116</v>
+        <v>0.004274534</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.007376719</v>
+        <v>0.001901579</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8902,26 +8902,26 @@
         <v>0.057567068</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.0541484</v>
+        <v>0.054154735</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050699858</v>
+        <v>0.050693543</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047504104</v>
+        <v>0.047515544</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044476116</v>
+        <v>0.04447563</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04169346</v>
+        <v>0.041693024</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039121314</v>
+        <v>0.039120921</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036977111</v>
+        <v>0.036976754</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9033,23 +9033,23 @@
         <v>5.95264624</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.844851763</v>
+        <v>0.844951923</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.450947391</v>
+        <v>0.45092291</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.304770814</v>
+        <v>0.30475941</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.228706625</v>
+        <v>0.228700066</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181934882</v>
+        <v>0.181953975</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.151165087</v>
+        <v>0.151178863</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094251075479077</v>
+        <v>0.2094414893617021</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949453927547728</v>
+        <v>0.07949374851626177</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.4000494682166707</v>
+        <v>0.3999703176016622</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418576362903842</v>
+        <v>0.01418541598811362</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682426648205364</v>
+        <v>0.02682424235465481</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2310</v>
+        <v>2230</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6584,7 +6584,7 @@
         <v>1801</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2285</v>
+        <v>2190</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2343</v>
+        <v>2324.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2310</v>
+        <v>2230</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41859,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.62</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="32">
@@ -41869,7 +41869,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.5</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -428억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -429억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -506억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -507억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -428억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -429억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -506억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -507억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 20.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
+          <t>· 세율 20.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2230</v>
+        <v>2200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6584,7 +6584,7 @@
         <v>1801</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2190</v>
+        <v>2150</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2324.2</v>
+        <v>2314.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.333351684</v>
+        <v>0.333215567</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.26139971</v>
+        <v>0.260688623</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.13838773</v>
+        <v>0.137753637</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.15339904</v>
+        <v>0.152732787</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210603328</v>
+        <v>0.210103004</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252694293</v>
+        <v>0.252803645</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.26398041</v>
+        <v>0.264138047</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252947972</v>
+        <v>0.253193822</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036887059</v>
+        <v>0.036879481</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036885563</v>
+        <v>0.036884249</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036888735</v>
+        <v>0.036888263</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036889491</v>
+        <v>0.036880917</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036888164</v>
+        <v>0.036888435</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036883438</v>
+        <v>0.036883365</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036883985</v>
+        <v>0.036883303</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036882184</v>
+        <v>0.036888309</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004752091</v>
+        <v>-0.005551127</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006136873</v>
+        <v>0.005336598</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.0008438779999999999</v>
+        <v>-0.009519283</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.000273465</v>
+        <v>0.003707072</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.001711853</v>
+        <v>0.001647216</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.005459849</v>
+        <v>-0.009140911</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.004593767</v>
+        <v>0.007801071</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.002701832</v>
+        <v>-0.009596812999999999</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.007540562</v>
+        <v>0.000538047</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.008288373</v>
+        <v>0.002579829</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.002698978</v>
+        <v>0.003500113</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.002048252</v>
+        <v>-0.001194358</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.001156982</v>
+        <v>-0.001133734</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.006408877</v>
+        <v>-0.001826434</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.004763514</v>
+        <v>-0.000605712</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.003593691</v>
+        <v>0.005130087</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.002800504</v>
+        <v>0.001970908</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.005768987</v>
+        <v>-0.000921222</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.004274534</v>
+        <v>-0.000795995</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.001901579</v>
+        <v>7.6235e-05</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8902,26 +8902,26 @@
         <v>0.057567068</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054154735</v>
+        <v>0.054167406</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050693543</v>
+        <v>0.050704953</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047515544</v>
+        <v>0.047514457</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.04447563</v>
+        <v>0.044485579</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041693024</v>
+        <v>0.041702172</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039120921</v>
+        <v>0.039129387</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036976754</v>
+        <v>0.036979798</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9030,26 +9030,26 @@
         <v>-1.200698812</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.95264624</v>
+        <v>5.954038997</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.844951923</v>
+        <v>0.844882836</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.45092291</v>
+        <v>0.450958042</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.30475941</v>
+        <v>0.304777225</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.228700066</v>
+        <v>0.228711509</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181953975</v>
+        <v>0.181915762</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.151178863</v>
+        <v>0.151191487</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2230</v>
+        <v>2200</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,365원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,300원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094414893617021</v>
+        <v>0.2094779682241528</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949374851626177</v>
+        <v>0.07949494349779335</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.3999703176016622</v>
+        <v>0.4000395980794931</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418541598811362</v>
+        <v>0.01418341974327973</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682424235465481</v>
+        <v>0.02682409884577916</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41859,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.91</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="32">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.39</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -429억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -428억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -507억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -506억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -429억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -428억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -507억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -506억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2200</v>
+        <v>2355</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2314.3</v>
+        <v>2324.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.333215567</v>
+        <v>0.333185319</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.260688623</v>
+        <v>0.261385768</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.137753637</v>
+        <v>0.138339874</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.152732787</v>
+        <v>0.153284168</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210103004</v>
+        <v>0.210640953</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252803645</v>
+        <v>0.252597604</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.264138047</v>
+        <v>0.263928448</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.253193822</v>
+        <v>0.252983127</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036879481</v>
+        <v>0.036880318</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036884249</v>
+        <v>0.036885971</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036888263</v>
+        <v>0.036890286</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036880917</v>
+        <v>0.036883205</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036888435</v>
+        <v>0.03688225</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036883365</v>
+        <v>0.036886693</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036883303</v>
+        <v>0.036887052</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036888309</v>
+        <v>0.036884822</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005551127</v>
+        <v>-0.005093801</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.005336598</v>
+        <v>0.005784516</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009519283</v>
+        <v>-0.009097966000000001</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.003707072</v>
+        <v>-7.886299999999999e-05</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.001647216</v>
+        <v>0.007889535</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.009140911</v>
+        <v>-0.002838034</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.007801071</v>
+        <v>-0.003760551</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>-0.009596812999999999</v>
+        <v>0.006819461</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.000538047</v>
+        <v>-0.002998873</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.002579829</v>
+        <v>0.001175397</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.003500113</v>
+        <v>0.001921904</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001194358</v>
+        <v>-0.002860014</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.001133734</v>
+        <v>-0.002818211</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.001826434</v>
+        <v>-0.00724098</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.000605712</v>
+        <v>0.003868245</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.005130087</v>
+        <v>-0.000512089</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001970908</v>
+        <v>-0.006992555</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.000921222</v>
+        <v>0.003121652</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.000795995</v>
+        <v>0.003069621</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>7.6235e-05</v>
+        <v>-0.009357245</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8902,26 +8902,26 @@
         <v>0.057567068</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054167406</v>
+        <v>0.054154735</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050704953</v>
+        <v>0.050699553</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047514457</v>
+        <v>0.047509552</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044485579</v>
+        <v>0.04448109</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041702172</v>
+        <v>0.041692806</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039129387</v>
+        <v>0.039125743</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036979798</v>
+        <v>0.036976397</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9030,26 +9030,26 @@
         <v>-1.200698812</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.954038997</v>
+        <v>5.953342618</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.844882836</v>
+        <v>0.844767151</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.450958042</v>
+        <v>0.450977199</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.304777225</v>
+        <v>0.304748008</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.228711509</v>
+        <v>0.228722184</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181915762</v>
+        <v>0.181922143</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.151191487</v>
+        <v>0.151175878</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2200</v>
+        <v>2355</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,255원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094779682241528</v>
+        <v>0.209457873738559</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949494349779335</v>
+        <v>0.07949391380905041</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.4000395980794931</v>
+        <v>0.3999307307901638</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418341974327973</v>
+        <v>0.01418510792534701</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682409884577916</v>
+        <v>0.02682421470608035</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41859,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.64</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="32">
@@ -41869,7 +41869,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="33">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.34</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -428억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -429억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -506억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -507억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -428억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -429억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -506억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -507억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2355</v>
+        <v>2350</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6493,7 +6493,7 @@
         <v>2870</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>2410</v>
+        <v>2450</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2324.4</v>
+        <v>2320</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.333185319</v>
+        <v>0.340354121</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.261385768</v>
+        <v>0.265833551</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138339874</v>
+        <v>0.13862701</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153284168</v>
+        <v>0.150929308</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210640953</v>
+        <v>0.199923271</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252597604</v>
+        <v>0.242799079</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263928448</v>
+        <v>0.258009268</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252983127</v>
+        <v>0.250496542</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036880318</v>
+        <v>0.036886171</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036885971</v>
+        <v>0.036888541</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036890286</v>
+        <v>0.036880983</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036883205</v>
+        <v>0.036888805</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.03688225</v>
+        <v>0.036881007</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036886693</v>
+        <v>0.036887353</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036887052</v>
+        <v>0.036884219</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036884822</v>
+        <v>0.036882138</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005093801</v>
+        <v>-0.005444928</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.005784516</v>
+        <v>0.005465606</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009097966000000001</v>
+        <v>-0.007085991</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>-7.886299999999999e-05</v>
+        <v>0.004897543</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.007889535</v>
+        <v>-0.001659421</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.002838034</v>
+        <v>0.002305351</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.003760551</v>
+        <v>-0.004094112</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>0.006819461</v>
+        <v>0.004582749</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.002998873</v>
+        <v>-0.001411877</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.001175397</v>
+        <v>0.000246245</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.001921904</v>
+        <v>0.00354355</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.002860014</v>
+        <v>-0.001141752</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.002818211</v>
+        <v>-0.004153767</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>-0.00724098</v>
+        <v>0.002655191</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.003868245</v>
+        <v>-0.003926611</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.000512089</v>
+        <v>0.009708233</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.006992555</v>
+        <v>0.001210058</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>0.003121652</v>
+        <v>-0.001253022</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.003069621</v>
+        <v>0.002419876</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.009357245</v>
+        <v>-0.00686129</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.057567068</v>
+        <v>0.057473267</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054154735</v>
+        <v>0.054102515</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050699553</v>
+        <v>0.050700551</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047509552</v>
+        <v>0.047550399</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.04448109</v>
+        <v>0.044540073</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041692806</v>
+        <v>0.041772973</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039125743</v>
+        <v>0.039204665</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.036976397</v>
+        <v>0.037044728</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9027,29 +9027,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>-1.200698812</v>
+        <v>-1.198881901</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>5.953342618</v>
+        <v>6</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.844767151</v>
+        <v>0.8468025300000001</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.450977199</v>
+        <v>0.451891716</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.304748008</v>
+        <v>0.305365233</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.228722184</v>
+        <v>0.229169654</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.181922143</v>
+        <v>0.18226578</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.151175878</v>
+        <v>0.151403308</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2355</v>
+        <v>2350</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,255원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,225원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.209457873738559</v>
+        <v>0.2094599890273533</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949391380905041</v>
+        <v>0.07949469196772589</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.3999307307901638</v>
+        <v>0.4000396569672335</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418510792534701</v>
+        <v>0.01418310904794408</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682421470608035</v>
+        <v>0.02682490664816891</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41839,7 +41839,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>112</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="30">
@@ -41859,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.03</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="32">
@@ -41879,7 +41879,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0196</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="34">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.57</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/025550_model.xlsx
+++ b/argus/kship/models/025550_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 67417억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 69011억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72162억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 75834억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80393억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85242억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 90441억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 94674억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1776,49 +1776,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 67417억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 69011억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72162억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 75834억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80393억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85242억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 90441억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 94674억 × 비례계수 0.0132(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2148,7 +2148,7 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -100억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.87억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 -99억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2208,7 +2208,7 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -100억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -99억 × 1.42%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 1545억 × 2.68%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4563,7 +4563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 20.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
+          <t>· 세율 20.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 20.94% · 근거: 최근 12분기 유효세율 214.5% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 3분기(2025Q2~2026Q2)의 법인세/세전 중위 20.9%</t>
         </is>
       </c>
     </row>
@@ -5434,35 +5434,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5553,35 +5553,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5672,35 +5672,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5791,35 +5791,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5910,35 +5910,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6029,35 +6029,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6148,35 +6148,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6267,35 +6267,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6402,7 +6402,7 @@
         <v>2320</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2350</v>
+        <v>2170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6584,7 +6584,7 @@
         <v>1801</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2150</v>
+        <v>2120</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6675,7 +6675,7 @@
         <v>2177.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2320</v>
+        <v>2290.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6834,29 +6834,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.340354121</v>
+        <v>0.345904648</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.265833551</v>
+        <v>0.270127962</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.13862701</v>
+        <v>0.139620023</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.150929308</v>
+        <v>0.149861006</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.199923271</v>
+        <v>0.192457664</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.242799079</v>
+        <v>0.235183051</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.258009268</v>
+        <v>0.253301699</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.250496542</v>
+        <v>0.248441558</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7148,32 +7148,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.036886171</v>
+        <v>0.036880134</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.036888541</v>
+        <v>0.036884571</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.036880983</v>
+        <v>0.036880341</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.036888805</v>
+        <v>0.036883117</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.036881007</v>
+        <v>0.036883469</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.036887353</v>
+        <v>0.03688266</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.036884219</v>
+        <v>0.036881607</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.036882138</v>
+        <v>0.036889149</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8508,36 +8508,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005444928</v>
+        <v>-0.00479973</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.005465606</v>
+        <v>0.00613628</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.007085991</v>
+        <v>-0.003642348</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>0.004897543</v>
+        <v>-0.007155186</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.001659421</v>
+        <v>0.003304379</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.002305351</v>
+        <v>-0.007937911000000001</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.004094112</v>
+        <v>0.004048659</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>0.004582749</v>
+        <v>0.000978437</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001411877</v>
+        <v>-0.003096206</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.000246245</v>
+        <v>0.004152864</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8636,36 +8636,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00354355</v>
+        <v>0.004604662</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.001141752</v>
+        <v>-3.229e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004153767</v>
+        <v>-0.001915147</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.002655191</v>
+        <v>-0.001286664</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.003926611</v>
+        <v>0.006983819</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.009708233</v>
+        <v>-0.001407841</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001210058</v>
+        <v>-0.002477308</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.001253022</v>
+        <v>0.002440773</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.002419876</v>
+        <v>0.002969496</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.00686129</v>
+        <v>-4.324e-06</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.057473267</v>
+        <v>0.057399566</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.054102515</v>
+        <v>0.054049259</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.050700551</v>
+        <v>0.050694624</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.047550399</v>
+        <v>0.047573549</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.044540073</v>
+        <v>0.044577464</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.041772973</v>
+        <v>0.041822868</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.039204665</v>
+        <v>0.039255638</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.037044728</v>
+        <v>0.037087116</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9027,29 +9027,29 @@
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>-1.198881901</v>
+        <v>-1.197344514</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>6</v>
+        <v>6.041076487</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.8468025300000001</v>
+        <v>0.848119091</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.451891716</v>
+        <v>0.452541635</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.305365233</v>
+        <v>0.305856345</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.229169654</v>
+        <v>0.229513371</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.18226578</v>
+        <v>0.182516161</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.151403308</v>
+        <v>0.151562993</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9712,11 +9712,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2350</v>
+        <v>2170</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,225원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,245원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2094599890273533</v>
+        <v>0.20941997725401</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.07949469196772589</v>
+        <v>0.07949331361873258</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.4000396569672335</v>
+        <v>0.4000892945728743</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01418310904794408</v>
+        <v>0.01418389242964135</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02682490664816891</v>
+        <v>0.02682559874702388</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41839,7 +41839,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>112.4</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="30">
@@ -41859,7 +41859,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.91</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="32">
@@ -41869,7 +41869,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="33">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.54</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="37">
